--- a/ozone/multistate/MAE_stacked_VTZP_MS_1_90_10_split.xlsx
+++ b/ozone/multistate/MAE_stacked_VTZP_MS_1_90_10_split.xlsx
@@ -447,10 +447,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.06075426633327188</v>
+        <v>0.0612281471015306</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7217454720163653</v>
+        <v>0.6955680580216057</v>
       </c>
     </row>
     <row r="3">
@@ -460,10 +460,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07654519234343564</v>
+        <v>0.07806976333677947</v>
       </c>
       <c r="C3" t="n">
-        <v>2.161659265440111</v>
+        <v>2.038219494817983</v>
       </c>
     </row>
   </sheetData>
